--- a/data_output/ch4_preference.xlsx
+++ b/data_output/ch4_preference.xlsx
@@ -676,13 +676,13 @@
         </is>
       </c>
       <c r="Q3">
-        <v>77.22241938441923</v>
+        <v>77.21690797352014</v>
       </c>
       <c r="R3">
-        <v>89.72513004007835</v>
+        <v>89.73153423408978</v>
       </c>
       <c r="S3">
-        <v>10.27486995992164</v>
+        <v>10.26846576591021</v>
       </c>
       <c r="T3">
         <v>114</v>
@@ -706,22 +706,22 @@
         <v>0.0150014570882921</v>
       </c>
       <c r="AA3">
-        <v>91.81631842409898</v>
+        <v>91.82287187814624</v>
       </c>
       <c r="AB3">
-        <v>106.9101986300512</v>
+        <v>106.9178294203718</v>
       </c>
       <c r="AC3">
-        <v>76.72243821814685</v>
+        <v>76.72791433592074</v>
       </c>
       <c r="AD3">
-        <v>0.01610812603931561</v>
+        <v>0.01610927576809583</v>
       </c>
       <c r="AE3">
-        <v>0.0187561751982546</v>
+        <v>0.01875751393339857</v>
       </c>
       <c r="AF3">
-        <v>0.01346007688037664</v>
+        <v>0.01346103760279311</v>
       </c>
     </row>
     <row r="4">
@@ -988,13 +988,13 @@
         </is>
       </c>
       <c r="Q6">
-        <v>85.7458672235407</v>
+        <v>85.74213518672632</v>
       </c>
       <c r="R6">
-        <v>94.88160441196244</v>
+        <v>94.88573425594058</v>
       </c>
       <c r="S6">
-        <v>5.118395588037555</v>
+        <v>5.114265744059422</v>
       </c>
       <c r="T6">
         <v>114</v>
@@ -1018,22 +1018,22 @@
         <v>0.02677286776811701</v>
       </c>
       <c r="AA6">
-        <v>173.2803223411019</v>
+        <v>173.2878645902047</v>
       </c>
       <c r="AB6">
-        <v>201.7662437149532</v>
+        <v>201.7750258504553</v>
       </c>
       <c r="AC6">
-        <v>144.7944009672507</v>
+        <v>144.8007033299543</v>
       </c>
       <c r="AD6">
-        <v>0.03040005655107051</v>
+        <v>0.0304013797526675</v>
       </c>
       <c r="AE6">
-        <v>0.03539758661665846</v>
+        <v>0.03539912734218513</v>
       </c>
       <c r="AF6">
-        <v>0.02540252648548259</v>
+        <v>0.02540363216314988</v>
       </c>
     </row>
     <row r="7">
@@ -1300,13 +1300,13 @@
         </is>
       </c>
       <c r="Q9">
-        <v>71.34852733123208</v>
+        <v>71.34206891883071</v>
       </c>
       <c r="R9">
-        <v>95.66200973713919</v>
+        <v>95.67066977068447</v>
       </c>
       <c r="S9">
-        <v>4.337990262860812</v>
+        <v>4.329330229315535</v>
       </c>
       <c r="T9">
         <v>114</v>
@@ -1330,22 +1330,22 @@
         <v>0.03014603859258876</v>
       </c>
       <c r="AA9">
-        <v>196.7170874550622</v>
+        <v>196.7348957426047</v>
       </c>
       <c r="AB9">
-        <v>229.0558285794417</v>
+        <v>229.0765644093149</v>
       </c>
       <c r="AC9">
-        <v>164.3783463306827</v>
+        <v>164.3932270758945</v>
       </c>
       <c r="AD9">
-        <v>0.03451176972895828</v>
+        <v>0.03451489398993064</v>
       </c>
       <c r="AE9">
-        <v>0.04018523308411257</v>
+        <v>0.04018887094900261</v>
       </c>
       <c r="AF9">
-        <v>0.02883830637380399</v>
+        <v>0.02884091703085868</v>
       </c>
     </row>
     <row r="10">
@@ -1612,13 +1612,13 @@
         </is>
       </c>
       <c r="Q12">
-        <v>67.37326531760105</v>
+        <v>67.36630132791029</v>
       </c>
       <c r="R12">
-        <v>2.504455509702352</v>
+        <v>2.504714407727132</v>
       </c>
       <c r="S12">
-        <v>97.49554449029766</v>
+        <v>97.49528559227288</v>
       </c>
       <c r="T12">
         <v>234</v>
@@ -1642,22 +1642,22 @@
         <v>0.000540471854022742</v>
       </c>
       <c r="AA12">
-        <v>0.1895264132515087</v>
+        <v>0.1895460055396704</v>
       </c>
       <c r="AB12">
-        <v>0.2206830641234</v>
+        <v>0.2207058772295552</v>
       </c>
       <c r="AC12">
-        <v>0.1583697623796173</v>
+        <v>0.1583861338497856</v>
       </c>
       <c r="AD12">
-        <v>1.619883873944519e-05</v>
+        <v>1.620051329398892e-05</v>
       </c>
       <c r="AE12">
-        <v>1.886180035242735e-05</v>
+        <v>1.886375019056028e-05</v>
       </c>
       <c r="AF12">
-        <v>1.353587712646302e-05</v>
+        <v>1.353727639741757e-05</v>
       </c>
     </row>
     <row r="13">
@@ -1924,13 +1924,13 @@
         </is>
       </c>
       <c r="Q15">
-        <v>47.63061929919311</v>
+        <v>47.62267398295383</v>
       </c>
       <c r="R15">
-        <v>79.70549504099975</v>
+        <v>79.71879302095644</v>
       </c>
       <c r="S15">
-        <v>20.29450495900025</v>
+        <v>20.28120697904357</v>
       </c>
       <c r="T15">
         <v>234</v>
@@ -1954,22 +1954,22 @@
         <v>0.004336644104182739</v>
       </c>
       <c r="AA15">
-        <v>48.39777388473377</v>
+        <v>48.40584851781567</v>
       </c>
       <c r="AB15">
-        <v>56.35398704802693</v>
+        <v>56.36338908724466</v>
       </c>
       <c r="AC15">
-        <v>40.44156072144062</v>
+        <v>40.44830794838669</v>
       </c>
       <c r="AD15">
-        <v>0.004136561870490066</v>
+        <v>0.004137252010069715</v>
       </c>
       <c r="AE15">
-        <v>0.004816580089574952</v>
+        <v>0.004817383682670483</v>
       </c>
       <c r="AF15">
-        <v>0.003456543651405181</v>
+        <v>0.003457120337468948</v>
       </c>
     </row>
     <row r="16">
@@ -2236,13 +2236,13 @@
         </is>
       </c>
       <c r="Q18">
-        <v>76.65318391628128</v>
+        <v>76.64757519217143</v>
       </c>
       <c r="R18">
-        <v>1.814971163726218</v>
+        <v>1.815103975136091</v>
       </c>
       <c r="S18">
-        <v>98.18502883627379</v>
+        <v>98.18489602486392</v>
       </c>
       <c r="T18">
         <v>234</v>
@@ -2266,22 +2266,22 @@
         <v>0.0004580343097851766</v>
       </c>
       <c r="AA18">
-        <v>0.1163994908082206</v>
+        <v>0.1164080083983575</v>
       </c>
       <c r="AB18">
-        <v>0.1355346510983327</v>
+        <v>0.1355445689132594</v>
       </c>
       <c r="AC18">
-        <v>0.09726433051810843</v>
+        <v>0.09727144788345543</v>
       </c>
       <c r="AD18">
-        <v>9.948674428053042e-06</v>
+        <v>9.949402427210039e-06</v>
       </c>
       <c r="AE18">
-        <v>1.158415821353271e-05</v>
+        <v>1.158500589002217e-05</v>
       </c>
       <c r="AF18">
-        <v>8.313190642573371e-06</v>
+        <v>8.3137989643979e-06</v>
       </c>
     </row>
     <row r="19">
@@ -2548,7 +2548,7 @@
         </is>
       </c>
       <c r="Q21">
-        <v>53.10134148837145</v>
+        <v>53.09340658390826</v>
       </c>
       <c r="R21">
         <v>100</v>
@@ -2860,13 +2860,13 @@
         </is>
       </c>
       <c r="Q24">
-        <v>36.25617909192961</v>
+        <v>36.24884477096424</v>
       </c>
       <c r="R24">
-        <v>90.94985522480847</v>
+        <v>90.96825734035691</v>
       </c>
       <c r="S24">
-        <v>9.050144775191525</v>
+        <v>9.031742659643086</v>
       </c>
       <c r="T24">
         <v>114</v>
@@ -2890,22 +2890,22 @@
         <v>0.01539696837394777</v>
       </c>
       <c r="AA24">
-        <v>95.52335426267531</v>
+        <v>95.54268174591728</v>
       </c>
       <c r="AB24">
-        <v>111.2266419881949</v>
+        <v>111.2491467575854</v>
       </c>
       <c r="AC24">
-        <v>79.82006653715572</v>
+        <v>79.83621673424918</v>
       </c>
       <c r="AD24">
-        <v>0.01675848320397812</v>
+        <v>0.0167618739905118</v>
       </c>
       <c r="AE24">
-        <v>0.01951344596284121</v>
+        <v>0.01951739416799743</v>
       </c>
       <c r="AF24">
-        <v>0.01400352044511504</v>
+        <v>0.01400635381302617</v>
       </c>
     </row>
     <row r="25">
@@ -3172,13 +3172,13 @@
         </is>
       </c>
       <c r="Q27">
-        <v>37.77578492931622</v>
+        <v>37.76831910575687</v>
       </c>
       <c r="R27">
-        <v>91.88476368685524</v>
+        <v>91.90292693715919</v>
       </c>
       <c r="S27">
-        <v>8.115236313144774</v>
+        <v>8.097073062840805</v>
       </c>
       <c r="T27">
         <v>114</v>
@@ -3202,22 +3202,22 @@
         <v>0.01246565573169529</v>
       </c>
       <c r="AA27">
-        <v>78.13236418772928</v>
+        <v>78.1478089429927</v>
       </c>
       <c r="AB27">
-        <v>90.97671000227328</v>
+        <v>90.99469375376044</v>
       </c>
       <c r="AC27">
-        <v>65.28801837318531</v>
+        <v>65.30092413222499</v>
       </c>
       <c r="AD27">
-        <v>0.01370743231363671</v>
+        <v>0.01371014191982328</v>
       </c>
       <c r="AE27">
-        <v>0.0159608263161883</v>
+        <v>0.01596398136030885</v>
       </c>
       <c r="AF27">
-        <v>0.01145403831108514</v>
+        <v>0.01145630247933772</v>
       </c>
     </row>
     <row r="28">
